--- a/docs/03-dane/fixtures/anonymized/xtb/xtb-syntetyczny-nowy-szablon-PLN.xlsx
+++ b/docs/03-dane/fixtures/anonymized/xtb/xtb-syntetyczny-nowy-szablon-PLN.xlsx
@@ -764,7 +764,7 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45901.66856481481</v>
+        <v>45902.66856481481</v>
       </c>
       <c r="E13" t="n">
         <v>11107.26</v>
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45901.66856481481</v>
+        <v>45902.66856481481</v>
       </c>
       <c r="E14" t="n">
         <v>-1083.63</v>
@@ -846,7 +846,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SEC FEE 2025-09-01</t>
+          <t>SEC FEE 2025-09-02</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
